--- a/output/pdf_financials_xlsx/DEMC.xlsx
+++ b/output/pdf_financials_xlsx/DEMC.xlsx
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.1773</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.326489</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.326489</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.326489</v>
       </c>
     </row>
     <row r="93">
@@ -3436,7 +3436,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3714,7 +3718,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.1773</v>
       </c>

--- a/output/pdf_financials_xlsx/DEMC.xlsx
+++ b/output/pdf_financials_xlsx/DEMC.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.034114</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.07713399999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.010893</v>
       </c>
     </row>
     <row r="13">
@@ -967,13 +967,13 @@
         <v>-0.500613</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.369751</v>
+        <v>-3.403865</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.666778</v>
+        <v>-7.743912</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.515299</v>
+        <v>-2.526192</v>
       </c>
     </row>
     <row r="28">
@@ -1005,13 +1005,13 @@
         <v>-0.489817</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.348161</v>
+        <v>-3.382275</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.666778</v>
+        <v>-7.743912</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.515299</v>
+        <v>-2.526192</v>
       </c>
     </row>
     <row r="30">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.070508</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.000012</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.602695</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.767051</v>
       </c>
     </row>
     <row r="35">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.070508</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.000012</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.602695</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.767051</v>
       </c>
     </row>
     <row r="37">
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.071945</v>
+        <v>0.001437</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.049669</v>
+        <v>0.049657</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.604229</v>
+        <v>0.001534</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.777281</v>
+        <v>0.01023</v>
       </c>
     </row>
     <row r="49">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5000,7 +5000,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>-0.012</v>
       </c>
@@ -5560,7 +5564,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6162,7 +6166,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
